--- a/depo.XLSX
+++ b/depo.XLSX
@@ -15,13 +15,13 @@
     <t>Операции в банкомате для ОБ УТУ</t>
   </si>
   <si>
-    <t>№ терминала: AM010201</t>
-  </si>
-  <si>
-    <t>Дата начала: 31/03/2023 13:35:16</t>
-  </si>
-  <si>
-    <t>Дата окончания: 13/04/2023 13:28:34</t>
+    <t>№ терминала: AM010070</t>
+  </si>
+  <si>
+    <t>Дата начала: 17/03/2023 12:09:45</t>
+  </si>
+  <si>
+    <t>Дата окончания: 27/03/2023 12:57:42</t>
   </si>
   <si>
     <t>Тип операции: CASH_IN</t>
@@ -57,673 +57,1177 @@
     <t>Responce</t>
   </si>
   <si>
-    <t>02/04/2023 07:39:25</t>
-  </si>
-  <si>
-    <t>000038</t>
-  </si>
-  <si>
-    <t>435303******2263</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>04/04/2023 07:19:50</t>
-  </si>
-  <si>
-    <t>000097</t>
-  </si>
-  <si>
-    <t>435303******4630</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>04/04/2023 15:39:05</t>
-  </si>
-  <si>
-    <t>000133</t>
-  </si>
-  <si>
-    <t>539877******8435</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 10:14:36</t>
-  </si>
-  <si>
-    <t>000185</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 10:15:51</t>
-  </si>
-  <si>
-    <t>000187</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 10:17:11</t>
-  </si>
-  <si>
-    <t>000189</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 10:18:33</t>
-  </si>
-  <si>
-    <t>000191</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 10:19:55</t>
-  </si>
-  <si>
-    <t>000193</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 14:46:48</t>
-  </si>
-  <si>
-    <t>000205</t>
-  </si>
-  <si>
-    <t>539877******5188</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>05/04/2023 15:28:10</t>
-  </si>
-  <si>
-    <t>000226</t>
-  </si>
-  <si>
-    <t>435303******4630</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>06/04/2023 07:15:35</t>
-  </si>
-  <si>
-    <t>000249</t>
-  </si>
-  <si>
-    <t>435303******2263</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>06/04/2023 16:19:06</t>
-  </si>
-  <si>
-    <t>000272</t>
-  </si>
-  <si>
-    <t>539877******8917</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>06/04/2023 18:30:10</t>
-  </si>
-  <si>
-    <t>000279</t>
-  </si>
-  <si>
-    <t>539877******3891</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>10/04/2023 14:14:34</t>
-  </si>
-  <si>
-    <t>000383</t>
-  </si>
-  <si>
-    <t>220038******3711</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>10/04/2023 17:24:16</t>
-  </si>
-  <si>
-    <t>000403</t>
-  </si>
-  <si>
-    <t>435303******2263</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>10/04/2023 19:23:52</t>
-  </si>
-  <si>
-    <t>000406</t>
-  </si>
-  <si>
-    <t>539877******5950</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>11/04/2023 06:42:06</t>
-  </si>
-  <si>
-    <t>000411</t>
-  </si>
-  <si>
-    <t>435303******4003</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>11/04/2023 06:56:54</t>
-  </si>
-  <si>
-    <t>000418</t>
-  </si>
-  <si>
-    <t>435303******2344</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>11/04/2023 14:44:36</t>
-  </si>
-  <si>
-    <t>000449</t>
-  </si>
-  <si>
-    <t>435303******9470</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>11/04/2023 20:13:08</t>
-  </si>
-  <si>
-    <t>000462</t>
-  </si>
-  <si>
-    <t>435303******7031</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:42:43</t>
-  </si>
-  <si>
-    <t>000475</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:44:02</t>
-  </si>
-  <si>
-    <t>000477</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:45:47</t>
-  </si>
-  <si>
-    <t>000480</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:47:13</t>
-  </si>
-  <si>
-    <t>000482</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:48:34</t>
-  </si>
-  <si>
-    <t>000484</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:49:55</t>
+    <t>17/03/2023 16:14:23</t>
+  </si>
+  <si>
+    <t>000039</t>
+  </si>
+  <si>
+    <t>220038******3803</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>17/03/2023 16:36:14</t>
+  </si>
+  <si>
+    <t>000043</t>
+  </si>
+  <si>
+    <t>220038******0391</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>17/03/2023 17:13:33</t>
+  </si>
+  <si>
+    <t>000051</t>
+  </si>
+  <si>
+    <t>220038******2618</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 09:26:37</t>
+  </si>
+  <si>
+    <t>000100</t>
+  </si>
+  <si>
+    <t>356514******8790</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 09:51:43</t>
+  </si>
+  <si>
+    <t>000106</t>
+  </si>
+  <si>
+    <t>539877******2885</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 10:05:51</t>
+  </si>
+  <si>
+    <t>000110</t>
+  </si>
+  <si>
+    <t>220038******6052</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 11:02:21</t>
+  </si>
+  <si>
+    <t>000131</t>
+  </si>
+  <si>
+    <t>356514******2322</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 12:15:10</t>
+  </si>
+  <si>
+    <t>000163</t>
+  </si>
+  <si>
+    <t>539877******1552</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>18/03/2023 13:41:29</t>
+  </si>
+  <si>
+    <t>000180</t>
+  </si>
+  <si>
+    <t>539877******2444</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>19/03/2023 12:49:06</t>
+  </si>
+  <si>
+    <t>000234</t>
+  </si>
+  <si>
+    <t>539877******2773</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>19/03/2023 14:26:07</t>
+  </si>
+  <si>
+    <t>000239</t>
+  </si>
+  <si>
+    <t>220038******6617</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>19/03/2023 15:10:26</t>
+  </si>
+  <si>
+    <t>000247</t>
+  </si>
+  <si>
+    <t>435303******0941</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>19/03/2023 16:27:24</t>
+  </si>
+  <si>
+    <t>000258</t>
+  </si>
+  <si>
+    <t>220038******9576</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>19/03/2023 18:20:16</t>
+  </si>
+  <si>
+    <t>000268</t>
+  </si>
+  <si>
+    <t>539877******1926</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 11:15:35</t>
+  </si>
+  <si>
+    <t>000327</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 11:17:27</t>
+  </si>
+  <si>
+    <t>000330</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 11:19:15</t>
+  </si>
+  <si>
+    <t>000333</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 11:21:09</t>
+  </si>
+  <si>
+    <t>000336</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 11:22:38</t>
+  </si>
+  <si>
+    <t>000339</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 13:27:39</t>
+  </si>
+  <si>
+    <t>000356</t>
+  </si>
+  <si>
+    <t>539877******6740</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 14:54:45</t>
+  </si>
+  <si>
+    <t>000366</t>
+  </si>
+  <si>
+    <t>220038******3315</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>20/03/2023 17:15:03</t>
+  </si>
+  <si>
+    <t>000393</t>
+  </si>
+  <si>
+    <t>555947******1649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>21/03/2023 10:55:16</t>
+  </si>
+  <si>
+    <t>000473</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>21/03/2023 11:05:23</t>
+  </si>
+  <si>
+    <t>000481</t>
+  </si>
+  <si>
+    <t>220038******2895</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>21/03/2023 11:23:56</t>
   </si>
   <si>
     <t>000486</t>
   </si>
   <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:51:42</t>
-  </si>
-  <si>
-    <t>000489</t>
-  </si>
-  <si>
-    <t>539877******2434</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 07:56:54</t>
-  </si>
-  <si>
-    <t>000494</t>
-  </si>
-  <si>
-    <t>435303******9218</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 10:47:43</t>
-  </si>
-  <si>
-    <t>000507</t>
-  </si>
-  <si>
-    <t>539877******2918</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 10:59:44</t>
-  </si>
-  <si>
-    <t>000512</t>
-  </si>
-  <si>
-    <t>539877******2036</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>12/04/2023 11:01:00</t>
+    <t>220015******4560</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>21/03/2023 17:06:12</t>
   </si>
   <si>
     <t>000514</t>
   </si>
   <si>
-    <t>539877******2036</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>[-1] AUTHORIZED</t>
-  </si>
-  <si>
-    <t>13/04/2023 07:52:44</t>
-  </si>
-  <si>
-    <t>000550</t>
-  </si>
-  <si>
-    <t>539877******8917</t>
-  </si>
-  <si>
-    <t>RUR</t>
-  </si>
-  <si>
-    <t>[618] ATM cash deposit</t>
-  </si>
-  <si>
-    <t>220</t>
+    <t>539877******3738</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>21/03/2023 18:16:52</t>
+  </si>
+  <si>
+    <t>000520</t>
+  </si>
+  <si>
+    <t>220038******1304</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 10:42:07</t>
+  </si>
+  <si>
+    <t>000561</t>
+  </si>
+  <si>
+    <t>220038******2371</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 11:20:50</t>
+  </si>
+  <si>
+    <t>000567</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 11:22:14</t>
+  </si>
+  <si>
+    <t>000570</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 11:23:51</t>
+  </si>
+  <si>
+    <t>000573</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 11:49:37</t>
+  </si>
+  <si>
+    <t>000577</t>
+  </si>
+  <si>
+    <t>539877******9915</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 14:05:04</t>
+  </si>
+  <si>
+    <t>000624</t>
+  </si>
+  <si>
+    <t>220038******9518</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>22/03/2023 18:01:10</t>
+  </si>
+  <si>
+    <t>000672</t>
+  </si>
+  <si>
+    <t>220038******5912</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 08:14:55</t>
+  </si>
+  <si>
+    <t>000699</t>
+  </si>
+  <si>
+    <t>539877******3348</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 08:44:31</t>
+  </si>
+  <si>
+    <t>000713</t>
+  </si>
+  <si>
+    <t>220038******6123</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 08:47:06</t>
+  </si>
+  <si>
+    <t>000719</t>
+  </si>
+  <si>
+    <t>539877******8733</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 09:15:38</t>
+  </si>
+  <si>
+    <t>000732</t>
+  </si>
+  <si>
+    <t>220038******1588</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 11:36:50</t>
+  </si>
+  <si>
+    <t>000771</t>
+  </si>
+  <si>
+    <t>220015******3620</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 11:40:17</t>
+  </si>
+  <si>
+    <t>000777</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 12:24:39</t>
+  </si>
+  <si>
+    <t>000785</t>
+  </si>
+  <si>
+    <t>220038******6196</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>23/03/2023 19:40:33</t>
+  </si>
+  <si>
+    <t>000809</t>
+  </si>
+  <si>
+    <t>220038******6222</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>24/03/2023 11:39:56</t>
+  </si>
+  <si>
+    <t>000890</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>25/03/2023 11:55:33</t>
+  </si>
+  <si>
+    <t>001056</t>
+  </si>
+  <si>
+    <t>539877******1926</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>25/03/2023 14:21:48</t>
+  </si>
+  <si>
+    <t>001073</t>
+  </si>
+  <si>
+    <t>539877******2444</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>25/03/2023 18:34:16</t>
+  </si>
+  <si>
+    <t>001090</t>
+  </si>
+  <si>
+    <t>220038******9092</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>25/03/2023 19:53:26</t>
+  </si>
+  <si>
+    <t>001101</t>
+  </si>
+  <si>
+    <t>623446******5777</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>26/03/2023 12:46:49</t>
+  </si>
+  <si>
+    <t>001131</t>
+  </si>
+  <si>
+    <t>220038******8283</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>26/03/2023 13:17:07</t>
+  </si>
+  <si>
+    <t>001135</t>
+  </si>
+  <si>
+    <t>539877******9757</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>26/03/2023 17:02:33</t>
+  </si>
+  <si>
+    <t>001163</t>
+  </si>
+  <si>
+    <t>220039******9114</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 08:19:25</t>
+  </si>
+  <si>
+    <t>001208</t>
+  </si>
+  <si>
+    <t>539877******3612</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 10:18:20</t>
+  </si>
+  <si>
+    <t>001236</t>
+  </si>
+  <si>
+    <t>548048******3699</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 11:06:15</t>
+  </si>
+  <si>
+    <t>001255</t>
+  </si>
+  <si>
+    <t>555947******7037</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[618] ATM cash deposit</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 11:38:08</t>
+  </si>
+  <si>
+    <t>001267</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 11:39:42</t>
+  </si>
+  <si>
+    <t>001270</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>[-1] AUTHORIZED</t>
+  </si>
+  <si>
+    <t>27/03/2023 11:41:21</t>
+  </si>
+  <si>
+    <t>001273</t>
+  </si>
+  <si>
+    <t>547601******5649</t>
+  </si>
+  <si>
+    <t>RUR</t>
+  </si>
+  <si>
+    <t>[762] ATM self incassation</t>
+  </si>
+  <si>
+    <t>210</t>
   </si>
   <si>
     <t>[-1] AUTHORIZED</t>
@@ -920,10 +1424,10 @@
         <v>24</v>
       </c>
       <c r="D12" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E12" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>25</v>
@@ -949,10 +1453,10 @@
         <v>31</v>
       </c>
       <c r="D13" s="1">
-        <v>7100</v>
+        <v>30000</v>
       </c>
       <c r="E13" s="1">
-        <v>7100</v>
+        <v>30000</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -978,10 +1482,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="1">
-        <v>333500</v>
+        <v>4000</v>
       </c>
       <c r="E14" s="1">
-        <v>333500</v>
+        <v>4000</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>39</v>
@@ -1007,10 +1511,10 @@
         <v>45</v>
       </c>
       <c r="D15" s="1">
-        <v>169000</v>
+        <v>50000</v>
       </c>
       <c r="E15" s="1">
-        <v>169000</v>
+        <v>50000</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>46</v>
@@ -1036,10 +1540,10 @@
         <v>52</v>
       </c>
       <c r="D16" s="1">
-        <v>126000</v>
+        <v>35000</v>
       </c>
       <c r="E16" s="1">
-        <v>126000</v>
+        <v>35000</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>53</v>
@@ -1065,10 +1569,10 @@
         <v>59</v>
       </c>
       <c r="D17" s="1">
-        <v>165000</v>
+        <v>4000</v>
       </c>
       <c r="E17" s="1">
-        <v>165000</v>
+        <v>4000</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>60</v>
@@ -1094,10 +1598,10 @@
         <v>66</v>
       </c>
       <c r="D18" s="1">
-        <v>495000</v>
+        <v>3500</v>
       </c>
       <c r="E18" s="1">
-        <v>495000</v>
+        <v>3500</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>67</v>
@@ -1123,10 +1627,10 @@
         <v>73</v>
       </c>
       <c r="D19" s="1">
-        <v>24500</v>
+        <v>300</v>
       </c>
       <c r="E19" s="1">
-        <v>24500</v>
+        <v>300</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>74</v>
@@ -1152,10 +1656,10 @@
         <v>80</v>
       </c>
       <c r="D20" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="E20" s="1">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>81</v>
@@ -1181,10 +1685,10 @@
         <v>87</v>
       </c>
       <c r="D21" s="1">
-        <v>15000</v>
+        <v>1600</v>
       </c>
       <c r="E21" s="1">
-        <v>15000</v>
+        <v>1600</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>88</v>
@@ -1210,10 +1714,10 @@
         <v>94</v>
       </c>
       <c r="D22" s="1">
-        <v>150</v>
+        <v>8600</v>
       </c>
       <c r="E22" s="1">
-        <v>150</v>
+        <v>8600</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>95</v>
@@ -1239,10 +1743,10 @@
         <v>101</v>
       </c>
       <c r="D23" s="1">
-        <v>7300</v>
+        <v>1400</v>
       </c>
       <c r="E23" s="1">
-        <v>7300</v>
+        <v>1400</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>102</v>
@@ -1268,10 +1772,10 @@
         <v>108</v>
       </c>
       <c r="D24" s="1">
-        <v>5000</v>
+        <v>2750</v>
       </c>
       <c r="E24" s="1">
-        <v>5000</v>
+        <v>2750</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>109</v>
@@ -1297,10 +1801,10 @@
         <v>115</v>
       </c>
       <c r="D25" s="1">
-        <v>17000</v>
+        <v>190500</v>
       </c>
       <c r="E25" s="1">
-        <v>17000</v>
+        <v>190500</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>116</v>
@@ -1326,10 +1830,10 @@
         <v>122</v>
       </c>
       <c r="D26" s="1">
-        <v>23000</v>
+        <v>45400</v>
       </c>
       <c r="E26" s="1">
-        <v>23000</v>
+        <v>45400</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>123</v>
@@ -1355,10 +1859,10 @@
         <v>129</v>
       </c>
       <c r="D27" s="1">
-        <v>1000</v>
+        <v>15800</v>
       </c>
       <c r="E27" s="1">
-        <v>1000</v>
+        <v>15800</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>130</v>
@@ -1384,10 +1888,10 @@
         <v>136</v>
       </c>
       <c r="D28" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E28" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>137</v>
@@ -1413,10 +1917,10 @@
         <v>143</v>
       </c>
       <c r="D29" s="1">
-        <v>9000</v>
+        <v>8800</v>
       </c>
       <c r="E29" s="1">
-        <v>9000</v>
+        <v>8800</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>144</v>
@@ -1442,10 +1946,10 @@
         <v>150</v>
       </c>
       <c r="D30" s="1">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="E30" s="1">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>151</v>
@@ -1471,10 +1975,10 @@
         <v>157</v>
       </c>
       <c r="D31" s="1">
-        <v>182000</v>
+        <v>6000</v>
       </c>
       <c r="E31" s="1">
-        <v>182000</v>
+        <v>6000</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>158</v>
@@ -1500,10 +2004,10 @@
         <v>164</v>
       </c>
       <c r="D32" s="1">
-        <v>401000</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="1">
-        <v>401000</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>165</v>
@@ -1529,10 +2033,10 @@
         <v>171</v>
       </c>
       <c r="D33" s="1">
-        <v>92000</v>
+        <v>39000</v>
       </c>
       <c r="E33" s="1">
-        <v>92000</v>
+        <v>39000</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>172</v>
@@ -1558,10 +2062,10 @@
         <v>178</v>
       </c>
       <c r="D34" s="1">
-        <v>210000</v>
+        <v>5500</v>
       </c>
       <c r="E34" s="1">
-        <v>210000</v>
+        <v>5500</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>179</v>
@@ -1587,10 +2091,10 @@
         <v>185</v>
       </c>
       <c r="D35" s="1">
-        <v>490000</v>
+        <v>5000</v>
       </c>
       <c r="E35" s="1">
-        <v>490000</v>
+        <v>5000</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>186</v>
@@ -1616,10 +2120,10 @@
         <v>192</v>
       </c>
       <c r="D36" s="1">
-        <v>173000</v>
+        <v>13000</v>
       </c>
       <c r="E36" s="1">
-        <v>173000</v>
+        <v>13000</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>193</v>
@@ -1645,10 +2149,10 @@
         <v>199</v>
       </c>
       <c r="D37" s="1">
-        <v>142000</v>
+        <v>11000</v>
       </c>
       <c r="E37" s="1">
-        <v>142000</v>
+        <v>11000</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>200</v>
@@ -1674,10 +2178,10 @@
         <v>206</v>
       </c>
       <c r="D38" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E38" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>207</v>
@@ -1703,10 +2207,10 @@
         <v>213</v>
       </c>
       <c r="D39" s="1">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="E39" s="1">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>214</v>
@@ -1732,10 +2236,10 @@
         <v>220</v>
       </c>
       <c r="D40" s="1">
-        <v>21000</v>
+        <v>8300</v>
       </c>
       <c r="E40" s="1">
-        <v>21000</v>
+        <v>8300</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>221</v>
@@ -1761,10 +2265,10 @@
         <v>227</v>
       </c>
       <c r="D41" s="1">
-        <v>5000</v>
+        <v>77100</v>
       </c>
       <c r="E41" s="1">
-        <v>5000</v>
+        <v>77100</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>228</v>
@@ -1790,10 +2294,10 @@
         <v>234</v>
       </c>
       <c r="D42" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="E42" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>235</v>
@@ -1806,6 +2310,702 @@
       </c>
       <c r="I42" s="1" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D44" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E44" s="1">
+        <v>80000</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1250</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1250</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7000</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="1">
+        <v>8000</v>
+      </c>
+      <c r="E47" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="1">
+        <v>100</v>
+      </c>
+      <c r="E49" s="1">
+        <v>100</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D50" s="1">
+        <v>46400</v>
+      </c>
+      <c r="E50" s="1">
+        <v>46400</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4000</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D52" s="1">
+        <v>19000</v>
+      </c>
+      <c r="E52" s="1">
+        <v>19000</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D53" s="1">
+        <v>75600</v>
+      </c>
+      <c r="E53" s="1">
+        <v>75600</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1100</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1100</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D55" s="1">
+        <v>300</v>
+      </c>
+      <c r="E55" s="1">
+        <v>300</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D56" s="1">
+        <v>200</v>
+      </c>
+      <c r="E56" s="1">
+        <v>200</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D59" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D60" s="1">
+        <v>8000</v>
+      </c>
+      <c r="E60" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D61" s="1">
+        <v>4300</v>
+      </c>
+      <c r="E61" s="1">
+        <v>4300</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D62" s="1">
+        <v>20000</v>
+      </c>
+      <c r="E62" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D63" s="1">
+        <v>800</v>
+      </c>
+      <c r="E63" s="1">
+        <v>800</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D64" s="1">
+        <v>6850</v>
+      </c>
+      <c r="E64" s="1">
+        <v>6850</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D65" s="1">
+        <v>161700</v>
+      </c>
+      <c r="E65" s="1">
+        <v>161700</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D66" s="1">
+        <v>65400</v>
+      </c>
+      <c r="E66" s="1">
+        <v>65400</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
